--- a/基本設計/06_プロジェクト管理_画面基本設計書.xlsx
+++ b/基本設計/06_プロジェクト管理_画面基本設計書.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R57a14d471803401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Reae1b10677d5444f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R006f38d0084740a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rca811127df1a4686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R882a48b02fb84f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Rbf92003badef4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-008_プロジェクト一覧" sheetId="19" r:id="Rbc32e301a11d4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-009_プロジェクト登録" sheetId="20" r:id="Rfea8bf5191f740d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-010_プロジェクト編集" sheetId="21" r:id="R247e1822967143e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-011_プロジェクト詳細" sheetId="22" r:id="Rd01a4243cf604afe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-012_プロジェクトメンバー管理" sheetId="23" r:id="R70aff4b74de34d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Ra1719920c7a542d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rab1cb85af94743de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R90742cb77caa46ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R9f4f429e91fe4d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R8122a6805aee4ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Rf838edce37754051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-008_プロジェクト一覧" sheetId="19" r:id="R8e07063238374295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-009_プロジェクト登録" sheetId="20" r:id="Rd68b4f0953b54417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-010_プロジェクト編集" sheetId="21" r:id="R57f1a29639ac4480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-011_プロジェクト詳細" sheetId="22" r:id="Rc9f1906b827f4737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-012_プロジェクトメンバー管理" sheetId="23" r:id="R07a4db35d023415b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1689,10 +1689,7 @@
       <x:c r="F16" s="301"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1707,25 +1704,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="344" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="344"/>
-      <x:c r="D19" s="344"/>
-      <x:c r="E19" s="344"/>
-      <x:c r="F19" s="344"/>
-      <x:c r="G19" s="344"/>
-      <x:c r="H19" s="344"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="344"/>
-      <x:c r="C20" s="344"/>
-      <x:c r="D20" s="344"/>
-      <x:c r="E20" s="344"/>
-      <x:c r="F20" s="344"/>
-      <x:c r="G20" s="344"/>
-      <x:c r="H20" s="344"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="344"/>
@@ -3385,54 +3379,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5158,54 +5120,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10908,54 +10838,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -12504,54 +12402,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14057,54 +13923,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
